--- a/data/Челябинск_ТЭЦ.xlsx
+++ b/data/Челябинск_ТЭЦ.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20383"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10302"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/alisa/Documents/линк/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C86CEA8B-17E6-494D-85F3-9F6B51072CFF}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C33C456-9259-DC46-82DC-47A5FB6C8364}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="7185" activeTab="3" xr2:uid="{0235F75B-AC8A-4D00-8701-6D090B69C299}"/>
+    <workbookView xWindow="0" yWindow="680" windowWidth="19200" windowHeight="10240" activeTab="2" xr2:uid="{0235F75B-AC8A-4D00-8701-6D090B69C299}"/>
   </bookViews>
   <sheets>
     <sheet name="ННЗТ" sheetId="2" r:id="rId1"/>
@@ -66,7 +66,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="57">
   <si>
     <t>№ п/п</t>
   </si>
@@ -656,29 +656,29 @@
     </xf>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="88">
+  <cellXfs count="83">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="4" fontId="3" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="4" fontId="5" fillId="2" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="4" fontId="5" fillId="2" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="4" fontId="4" fillId="2" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="4" fontId="4" fillId="2" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="4" fontId="4" fillId="2" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="5" fillId="2" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="4" fontId="4" fillId="2" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="5" fillId="2" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="3" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="3" fontId="4" fillId="2" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="3" fontId="4" fillId="2" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="4" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -689,247 +689,232 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="4" fontId="4" fillId="2" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="4" fontId="4" fillId="2" borderId="3" xfId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="4" fontId="5" fillId="2" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="3" fontId="4" fillId="2" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="4" fontId="4" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="3" fontId="4" fillId="2" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="4" fontId="4" fillId="2" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="3" fontId="4" fillId="2" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="4" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="4" fontId="4" fillId="2" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="4" fontId="4" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="4" fontId="4" fillId="2" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="4" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="4" fontId="4" fillId="2" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="4" fillId="2" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="4" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="2" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="4" fontId="4" fillId="2" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="4" fillId="2" borderId="15" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="4" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="3" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="4" fontId="4" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="2" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="2" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="2" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="2" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="4" fillId="3" borderId="23" xfId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="3" fontId="4" fillId="3" borderId="12" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="4" fontId="4" fillId="3" borderId="24" xfId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="4" fillId="3" borderId="23" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="4" fontId="4" fillId="3" borderId="25" xfId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="4" fontId="4" fillId="3" borderId="24" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="4" fontId="4" fillId="2" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="4" fillId="2" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="4" fillId="2" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="4" fillId="2" borderId="15" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="2" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="2" borderId="15" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="3" borderId="3" xfId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="4" fontId="4" fillId="3" borderId="25" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="3" fontId="4" fillId="3" borderId="12" xfId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="4" fontId="4" fillId="2" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="2" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="4" fontId="4" fillId="2" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="3" fontId="4" fillId="2" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="4" fontId="4" fillId="2" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="4" fontId="4" fillId="2" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="4" fontId="4" fillId="2" borderId="15" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="4" fontId="4" fillId="2" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="2" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="2" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="2" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="2" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="4" fontId="4" fillId="2" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="4" fillId="2" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="4" fontId="4" fillId="3" borderId="14" xfId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="4" fontId="4" fillId="3" borderId="15" xfId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="4" fontId="4" fillId="3" borderId="20" xfId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="4" fontId="4" fillId="2" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="4" fontId="4" fillId="2" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="4" fillId="2" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="4" fillId="2" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="4" fillId="3" borderId="14" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="4" fontId="4" fillId="3" borderId="15" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="4" fontId="4" fillId="3" borderId="20" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="4" fontId="4" fillId="2" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="2" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="2" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="2" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="4" fillId="2" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="4" fillId="2" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="4" fillId="2" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -1249,43 +1234,43 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2A282F8-8996-4D35-843C-6F534F30B850}">
   <dimension ref="A1:E14"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="3" width="15.59765625" customWidth="1"/>
+    <col min="2" max="3" width="15.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A1" s="20" t="s">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A1" s="30" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="20" t="s">
+      <c r="B1" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="20" t="s">
+      <c r="C1" s="30" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="21" t="s">
+      <c r="D1" s="31" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="14" t="s">
+      <c r="E1" s="24" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A2" s="20"/>
-      <c r="B2" s="20"/>
-      <c r="C2" s="20"/>
-      <c r="D2" s="22"/>
-      <c r="E2" s="15"/>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A3" s="18">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A2" s="30"/>
+      <c r="B2" s="30"/>
+      <c r="C2" s="30"/>
+      <c r="D2" s="32"/>
+      <c r="E2" s="25"/>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A3" s="28">
         <v>1</v>
       </c>
-      <c r="B3" s="12" t="s">
+      <c r="B3" s="22" t="s">
         <v>48</v>
       </c>
-      <c r="C3" s="16" t="s">
+      <c r="C3" s="26" t="s">
         <v>49</v>
       </c>
       <c r="D3" s="3" t="s">
@@ -1295,10 +1280,10 @@
         <v>46674.103769945301</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A4" s="19"/>
-      <c r="B4" s="13"/>
-      <c r="C4" s="17"/>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A4" s="29"/>
+      <c r="B4" s="23"/>
+      <c r="C4" s="27"/>
       <c r="D4" s="3" t="s">
         <v>36</v>
       </c>
@@ -1306,10 +1291,10 @@
         <v>46454.695330984752</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A5" s="19"/>
-      <c r="B5" s="13"/>
-      <c r="C5" s="17"/>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A5" s="29"/>
+      <c r="B5" s="23"/>
+      <c r="C5" s="27"/>
       <c r="D5" s="3" t="s">
         <v>37</v>
       </c>
@@ -1317,10 +1302,10 @@
         <v>45920.190962701017</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A6" s="19"/>
-      <c r="B6" s="13"/>
-      <c r="C6" s="17"/>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A6" s="29"/>
+      <c r="B6" s="23"/>
+      <c r="C6" s="27"/>
       <c r="D6" s="3" t="s">
         <v>38</v>
       </c>
@@ -1328,10 +1313,10 @@
         <v>39902.226056</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A7" s="19"/>
-      <c r="B7" s="13"/>
-      <c r="C7" s="17"/>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A7" s="29"/>
+      <c r="B7" s="23"/>
+      <c r="C7" s="27"/>
       <c r="D7" s="3" t="s">
         <v>39</v>
       </c>
@@ -1339,10 +1324,10 @@
         <v>39444.904647914424</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A8" s="19"/>
-      <c r="B8" s="13"/>
-      <c r="C8" s="17"/>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A8" s="29"/>
+      <c r="B8" s="23"/>
+      <c r="C8" s="27"/>
       <c r="D8" s="3" t="s">
         <v>40</v>
       </c>
@@ -1350,10 +1335,10 @@
         <v>36576.710000372084</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A9" s="19"/>
-      <c r="B9" s="13"/>
-      <c r="C9" s="17"/>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A9" s="29"/>
+      <c r="B9" s="23"/>
+      <c r="C9" s="27"/>
       <c r="D9" s="3" t="s">
         <v>41</v>
       </c>
@@ -1361,10 +1346,10 @@
         <v>33307.986657073117</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A10" s="19"/>
-      <c r="B10" s="13"/>
-      <c r="C10" s="17"/>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A10" s="29"/>
+      <c r="B10" s="23"/>
+      <c r="C10" s="27"/>
       <c r="D10" s="3" t="s">
         <v>42</v>
       </c>
@@ -1372,10 +1357,10 @@
         <v>18725.236539027719</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A11" s="19"/>
-      <c r="B11" s="13"/>
-      <c r="C11" s="17"/>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A11" s="29"/>
+      <c r="B11" s="23"/>
+      <c r="C11" s="27"/>
       <c r="D11" s="3" t="s">
         <v>43</v>
       </c>
@@ -1383,10 +1368,10 @@
         <v>29594.216612992743</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A12" s="19"/>
-      <c r="B12" s="13"/>
-      <c r="C12" s="17"/>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A12" s="29"/>
+      <c r="B12" s="23"/>
+      <c r="C12" s="27"/>
       <c r="D12" s="3" t="s">
         <v>44</v>
       </c>
@@ -1394,10 +1379,10 @@
         <v>38626.409729214516</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A13" s="19"/>
-      <c r="B13" s="13"/>
-      <c r="C13" s="17"/>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A13" s="29"/>
+      <c r="B13" s="23"/>
+      <c r="C13" s="27"/>
       <c r="D13" s="3" t="s">
         <v>45</v>
       </c>
@@ -1405,10 +1390,10 @@
         <v>43589.103209302339</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A14" s="19"/>
-      <c r="B14" s="13"/>
-      <c r="C14" s="17"/>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A14" s="29"/>
+      <c r="B14" s="23"/>
+      <c r="C14" s="27"/>
       <c r="D14" s="3" t="s">
         <v>46</v>
       </c>
@@ -1434,171 +1419,171 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{678291B2-7CF0-4A97-A365-D8B57F134FC8}">
   <dimension ref="A1:AE14"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="3" max="3" width="20.59765625" customWidth="1"/>
-    <col min="4" max="4" width="15.59765625" customWidth="1"/>
-    <col min="6" max="6" width="15.59765625" customWidth="1"/>
-    <col min="7" max="7" width="35.59765625" customWidth="1"/>
-    <col min="8" max="9" width="70.59765625" customWidth="1"/>
-    <col min="10" max="10" width="80.59765625" customWidth="1"/>
-    <col min="11" max="11" width="70.59765625" customWidth="1"/>
-    <col min="12" max="15" width="60.59765625" customWidth="1"/>
-    <col min="16" max="16" width="50.59765625" customWidth="1"/>
-    <col min="17" max="18" width="20.59765625" customWidth="1"/>
-    <col min="19" max="19" width="30.59765625" customWidth="1"/>
-    <col min="20" max="20" width="20.59765625" customWidth="1"/>
-    <col min="21" max="21" width="30.59765625" customWidth="1"/>
-    <col min="22" max="22" width="70.59765625" customWidth="1"/>
-    <col min="23" max="23" width="20.59765625" customWidth="1"/>
-    <col min="24" max="24" width="30.59765625" customWidth="1"/>
-    <col min="25" max="25" width="20.59765625" customWidth="1"/>
-    <col min="26" max="26" width="40.59765625" customWidth="1"/>
-    <col min="27" max="27" width="30.59765625" customWidth="1"/>
-    <col min="28" max="28" width="50.59765625" customWidth="1"/>
-    <col min="29" max="29" width="40.59765625" customWidth="1"/>
-    <col min="30" max="30" width="50.59765625" customWidth="1"/>
+    <col min="3" max="3" width="20.6640625" customWidth="1"/>
+    <col min="4" max="4" width="15.6640625" customWidth="1"/>
+    <col min="6" max="6" width="15.6640625" customWidth="1"/>
+    <col min="7" max="7" width="35.6640625" customWidth="1"/>
+    <col min="8" max="9" width="70.6640625" customWidth="1"/>
+    <col min="10" max="10" width="80.6640625" customWidth="1"/>
+    <col min="11" max="11" width="70.6640625" customWidth="1"/>
+    <col min="12" max="15" width="60.6640625" customWidth="1"/>
+    <col min="16" max="16" width="50.6640625" customWidth="1"/>
+    <col min="17" max="18" width="20.6640625" customWidth="1"/>
+    <col min="19" max="19" width="30.6640625" customWidth="1"/>
+    <col min="20" max="20" width="20.6640625" customWidth="1"/>
+    <col min="21" max="21" width="30.6640625" customWidth="1"/>
+    <col min="22" max="22" width="70.6640625" customWidth="1"/>
+    <col min="23" max="23" width="20.6640625" customWidth="1"/>
+    <col min="24" max="24" width="30.6640625" customWidth="1"/>
+    <col min="25" max="25" width="20.6640625" customWidth="1"/>
+    <col min="26" max="26" width="40.6640625" customWidth="1"/>
+    <col min="27" max="27" width="30.6640625" customWidth="1"/>
+    <col min="28" max="28" width="50.6640625" customWidth="1"/>
+    <col min="29" max="29" width="40.6640625" customWidth="1"/>
+    <col min="30" max="30" width="50.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" ht="30" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="25" t="s">
+    <row r="1" spans="1:31" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="25" t="s">
+      <c r="B1" s="35" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="25" t="s">
+      <c r="C1" s="35" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="29" t="s">
+      <c r="D1" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="25" t="s">
+      <c r="E1" s="35" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="56" t="s">
+      <c r="F1" s="36" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="55" t="s">
+      <c r="G1" s="33" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="48" t="s">
+      <c r="H1" s="42" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="48" t="s">
+      <c r="I1" s="42" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="42" t="s">
+      <c r="J1" s="43" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="49" t="s">
+      <c r="K1" s="34" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="42" t="s">
+      <c r="L1" s="43" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="42" t="s">
+      <c r="M1" s="43" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="49" t="s">
+      <c r="N1" s="34" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="51" t="s">
+      <c r="O1" s="49" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="51" t="s">
+      <c r="P1" s="49" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="38" t="s">
+      <c r="Q1" s="39" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="38" t="s">
+      <c r="R1" s="39" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="38" t="s">
+      <c r="S1" s="39" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="38" t="s">
+      <c r="T1" s="39" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="38" t="s">
+      <c r="U1" s="39" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="42" t="s">
+      <c r="V1" s="43" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="46" t="s">
+      <c r="W1" s="59" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="42" t="s">
+      <c r="X1" s="43" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" s="38" t="s">
+      <c r="Y1" s="39" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" s="38" t="s">
+      <c r="Z1" s="39" t="s">
         <v>25</v>
       </c>
-      <c r="AA1" s="44" t="s">
+      <c r="AA1" s="37" t="s">
         <v>26</v>
       </c>
-      <c r="AB1" s="44" t="s">
+      <c r="AB1" s="37" t="s">
         <v>27</v>
       </c>
-      <c r="AC1" s="44" t="s">
+      <c r="AC1" s="37" t="s">
         <v>28</v>
       </c>
-      <c r="AD1" s="38" t="s">
+      <c r="AD1" s="39" t="s">
         <v>29</v>
       </c>
-      <c r="AE1" s="40" t="s">
+      <c r="AE1" s="57" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="2" spans="1:31" ht="30" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="26"/>
-      <c r="B2" s="25"/>
-      <c r="C2" s="25"/>
-      <c r="D2" s="30"/>
-      <c r="E2" s="56"/>
-      <c r="F2" s="57"/>
-      <c r="G2" s="49"/>
-      <c r="H2" s="48"/>
-      <c r="I2" s="48"/>
-      <c r="J2" s="43"/>
-      <c r="K2" s="50"/>
-      <c r="L2" s="43"/>
-      <c r="M2" s="43"/>
-      <c r="N2" s="50"/>
-      <c r="O2" s="51"/>
-      <c r="P2" s="51"/>
-      <c r="Q2" s="39"/>
-      <c r="R2" s="39"/>
-      <c r="S2" s="39"/>
-      <c r="T2" s="39"/>
-      <c r="U2" s="39"/>
-      <c r="V2" s="43"/>
-      <c r="W2" s="47"/>
-      <c r="X2" s="43"/>
-      <c r="Y2" s="39"/>
-      <c r="Z2" s="39"/>
-      <c r="AA2" s="45"/>
-      <c r="AB2" s="45"/>
-      <c r="AC2" s="45"/>
-      <c r="AD2" s="39"/>
-      <c r="AE2" s="41"/>
-    </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.45">
-      <c r="A3" s="23">
+    <row r="2" spans="1:31" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="35"/>
+      <c r="B2" s="35"/>
+      <c r="C2" s="35"/>
+      <c r="D2" s="18"/>
+      <c r="E2" s="36"/>
+      <c r="F2" s="41"/>
+      <c r="G2" s="34"/>
+      <c r="H2" s="42"/>
+      <c r="I2" s="42"/>
+      <c r="J2" s="44"/>
+      <c r="K2" s="45"/>
+      <c r="L2" s="44"/>
+      <c r="M2" s="44"/>
+      <c r="N2" s="45"/>
+      <c r="O2" s="49"/>
+      <c r="P2" s="49"/>
+      <c r="Q2" s="40"/>
+      <c r="R2" s="40"/>
+      <c r="S2" s="40"/>
+      <c r="T2" s="40"/>
+      <c r="U2" s="40"/>
+      <c r="V2" s="44"/>
+      <c r="W2" s="60"/>
+      <c r="X2" s="44"/>
+      <c r="Y2" s="40"/>
+      <c r="Z2" s="40"/>
+      <c r="AA2" s="38"/>
+      <c r="AB2" s="38"/>
+      <c r="AC2" s="38"/>
+      <c r="AD2" s="40"/>
+      <c r="AE2" s="58"/>
+    </row>
+    <row r="3" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A3" s="61">
         <v>1</v>
       </c>
-      <c r="B3" s="36" t="s">
+      <c r="B3" s="55" t="s">
         <v>31</v>
       </c>
-      <c r="C3" s="34" t="s">
+      <c r="C3" s="53" t="s">
         <v>32</v>
       </c>
-      <c r="D3" s="27" t="s">
+      <c r="D3" s="63" t="s">
         <v>33</v>
       </c>
       <c r="E3" s="3" t="s">
@@ -1607,7 +1592,7 @@
       <c r="F3" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="G3" s="31">
+      <c r="G3" s="50">
         <v>4300</v>
       </c>
       <c r="H3" s="1">
@@ -1634,7 +1619,7 @@
       <c r="O3" s="4">
         <v>4095.8907389952001</v>
       </c>
-      <c r="P3" s="52">
+      <c r="P3" s="46">
         <v>7</v>
       </c>
       <c r="Q3" s="4">
@@ -1646,10 +1631,10 @@
       <c r="S3" s="4">
         <v>0.2</v>
       </c>
-      <c r="T3" s="31">
+      <c r="T3" s="50">
         <v>1</v>
       </c>
-      <c r="U3" s="31">
+      <c r="U3" s="50">
         <v>4300</v>
       </c>
       <c r="V3" s="1">
@@ -1683,18 +1668,18 @@
         <v>3958.58</v>
       </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.45">
-      <c r="A4" s="24"/>
-      <c r="B4" s="37"/>
-      <c r="C4" s="35"/>
-      <c r="D4" s="28"/>
+    <row r="4" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A4" s="62"/>
+      <c r="B4" s="56"/>
+      <c r="C4" s="54"/>
+      <c r="D4" s="64"/>
       <c r="E4" s="3" t="s">
         <v>36</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="G4" s="32"/>
+      <c r="G4" s="51"/>
       <c r="H4" s="1">
         <v>257.7</v>
       </c>
@@ -1719,7 +1704,7 @@
       <c r="O4" s="4">
         <v>4076.6365290456006</v>
       </c>
-      <c r="P4" s="53"/>
+      <c r="P4" s="47"/>
       <c r="Q4" s="4">
         <v>46454.695330984752</v>
       </c>
@@ -1727,8 +1712,8 @@
         <v>0.15</v>
       </c>
       <c r="S4" s="4"/>
-      <c r="T4" s="32"/>
-      <c r="U4" s="32"/>
+      <c r="T4" s="51"/>
+      <c r="U4" s="51"/>
       <c r="V4" s="1">
         <v>0.41</v>
       </c>
@@ -1758,18 +1743,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.45">
-      <c r="A5" s="24"/>
-      <c r="B5" s="37"/>
-      <c r="C5" s="35"/>
-      <c r="D5" s="28"/>
+    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A5" s="62"/>
+      <c r="B5" s="56"/>
+      <c r="C5" s="54"/>
+      <c r="D5" s="64"/>
       <c r="E5" s="3" t="s">
         <v>37</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="G5" s="32"/>
+      <c r="G5" s="51"/>
       <c r="H5" s="1">
         <v>259.10000000000002</v>
       </c>
@@ -1794,7 +1779,7 @@
       <c r="O5" s="4">
         <v>4029.7310436655998</v>
       </c>
-      <c r="P5" s="53"/>
+      <c r="P5" s="47"/>
       <c r="Q5" s="4">
         <v>45920.190962701017</v>
       </c>
@@ -1802,8 +1787,8 @@
         <v>0.15</v>
       </c>
       <c r="S5" s="4"/>
-      <c r="T5" s="32"/>
-      <c r="U5" s="32"/>
+      <c r="T5" s="51"/>
+      <c r="U5" s="51"/>
       <c r="V5" s="1">
         <v>0.12</v>
       </c>
@@ -1833,18 +1818,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.45">
-      <c r="A6" s="24"/>
-      <c r="B6" s="37"/>
-      <c r="C6" s="35"/>
-      <c r="D6" s="28"/>
+    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A6" s="62"/>
+      <c r="B6" s="56"/>
+      <c r="C6" s="54"/>
+      <c r="D6" s="64"/>
       <c r="E6" s="3" t="s">
         <v>38</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="G6" s="32"/>
+      <c r="G6" s="51"/>
       <c r="H6" s="1">
         <v>309.89999999999998</v>
       </c>
@@ -1869,7 +1854,7 @@
       <c r="O6" s="4">
         <v>3501.6239191999998</v>
       </c>
-      <c r="P6" s="53"/>
+      <c r="P6" s="47"/>
       <c r="Q6" s="4">
         <v>39902.226056</v>
       </c>
@@ -1877,8 +1862,8 @@
         <v>0</v>
       </c>
       <c r="S6" s="4"/>
-      <c r="T6" s="32"/>
-      <c r="U6" s="32"/>
+      <c r="T6" s="51"/>
+      <c r="U6" s="51"/>
       <c r="V6" s="1">
         <v>0.22</v>
       </c>
@@ -1908,18 +1893,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.45">
-      <c r="A7" s="24"/>
-      <c r="B7" s="37"/>
-      <c r="C7" s="35"/>
-      <c r="D7" s="28"/>
+    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A7" s="62"/>
+      <c r="B7" s="56"/>
+      <c r="C7" s="54"/>
+      <c r="D7" s="64"/>
       <c r="E7" s="3" t="s">
         <v>39</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="G7" s="32"/>
+      <c r="G7" s="51"/>
       <c r="H7" s="1">
         <v>375.1</v>
       </c>
@@ -1944,7 +1929,7 @@
       <c r="O7" s="4">
         <v>3461.4916323680004</v>
       </c>
-      <c r="P7" s="53"/>
+      <c r="P7" s="47"/>
       <c r="Q7" s="4">
         <v>39444.904647914424</v>
       </c>
@@ -1952,8 +1937,8 @@
         <v>0.15</v>
       </c>
       <c r="S7" s="4"/>
-      <c r="T7" s="32"/>
-      <c r="U7" s="32"/>
+      <c r="T7" s="51"/>
+      <c r="U7" s="51"/>
       <c r="V7" s="1">
         <v>0.28999999999999998</v>
       </c>
@@ -1983,18 +1968,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.45">
-      <c r="A8" s="24"/>
-      <c r="B8" s="37"/>
-      <c r="C8" s="35"/>
-      <c r="D8" s="28"/>
+    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A8" s="62"/>
+      <c r="B8" s="56"/>
+      <c r="C8" s="54"/>
+      <c r="D8" s="64"/>
       <c r="E8" s="3" t="s">
         <v>40</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="G8" s="32"/>
+      <c r="G8" s="51"/>
       <c r="H8" s="1">
         <v>389.4</v>
       </c>
@@ -2019,7 +2004,7 @@
       <c r="O8" s="4">
         <v>3209.7929183999995</v>
       </c>
-      <c r="P8" s="53"/>
+      <c r="P8" s="47"/>
       <c r="Q8" s="4">
         <v>36576.710000372084</v>
       </c>
@@ -2027,8 +2012,8 @@
         <v>0.15</v>
       </c>
       <c r="S8" s="4"/>
-      <c r="T8" s="32"/>
-      <c r="U8" s="32"/>
+      <c r="T8" s="51"/>
+      <c r="U8" s="51"/>
       <c r="V8" s="1">
         <v>0.31</v>
       </c>
@@ -2058,18 +2043,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.45">
-      <c r="A9" s="24"/>
-      <c r="B9" s="37"/>
-      <c r="C9" s="35"/>
-      <c r="D9" s="28"/>
+    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A9" s="62"/>
+      <c r="B9" s="56"/>
+      <c r="C9" s="54"/>
+      <c r="D9" s="64"/>
       <c r="E9" s="3" t="s">
         <v>41</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="G9" s="32"/>
+      <c r="G9" s="51"/>
       <c r="H9" s="1">
         <v>394.6</v>
       </c>
@@ -2094,7 +2079,7 @@
       <c r="O9" s="4">
         <v>2922.9457678655999</v>
       </c>
-      <c r="P9" s="53"/>
+      <c r="P9" s="47"/>
       <c r="Q9" s="4">
         <v>33307.986657073117</v>
       </c>
@@ -2102,8 +2087,8 @@
         <v>0.15</v>
       </c>
       <c r="S9" s="4"/>
-      <c r="T9" s="32"/>
-      <c r="U9" s="32"/>
+      <c r="T9" s="51"/>
+      <c r="U9" s="51"/>
       <c r="V9" s="1">
         <v>0.23</v>
       </c>
@@ -2133,18 +2118,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.45">
-      <c r="A10" s="24"/>
-      <c r="B10" s="37"/>
-      <c r="C10" s="35"/>
-      <c r="D10" s="28"/>
+    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A10" s="62"/>
+      <c r="B10" s="56"/>
+      <c r="C10" s="54"/>
+      <c r="D10" s="64"/>
       <c r="E10" s="3" t="s">
         <v>42</v>
       </c>
       <c r="F10" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="G10" s="32"/>
+      <c r="G10" s="51"/>
       <c r="H10" s="1">
         <v>388.6</v>
       </c>
@@ -2169,7 +2154,7 @@
       <c r="O10" s="4">
         <v>1643.2350432208</v>
       </c>
-      <c r="P10" s="53"/>
+      <c r="P10" s="47"/>
       <c r="Q10" s="4">
         <v>18725.236539027719</v>
       </c>
@@ -2177,8 +2162,8 @@
         <v>0.15</v>
       </c>
       <c r="S10" s="4"/>
-      <c r="T10" s="32"/>
-      <c r="U10" s="32"/>
+      <c r="T10" s="51"/>
+      <c r="U10" s="51"/>
       <c r="V10" s="1">
         <v>0.2</v>
       </c>
@@ -2208,18 +2193,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.45">
-      <c r="A11" s="24"/>
-      <c r="B11" s="37"/>
-      <c r="C11" s="35"/>
-      <c r="D11" s="28"/>
+    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A11" s="62"/>
+      <c r="B11" s="56"/>
+      <c r="C11" s="54"/>
+      <c r="D11" s="64"/>
       <c r="E11" s="3" t="s">
         <v>43</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="G11" s="32"/>
+      <c r="G11" s="51"/>
       <c r="H11" s="1">
         <v>382.8</v>
       </c>
@@ -2244,7 +2229,7 @@
       <c r="O11" s="4">
         <v>2597.0434986912001</v>
       </c>
-      <c r="P11" s="53"/>
+      <c r="P11" s="47"/>
       <c r="Q11" s="4">
         <v>29594.216612992743</v>
       </c>
@@ -2252,8 +2237,8 @@
         <v>0</v>
       </c>
       <c r="S11" s="4"/>
-      <c r="T11" s="32"/>
-      <c r="U11" s="32"/>
+      <c r="T11" s="51"/>
+      <c r="U11" s="51"/>
       <c r="V11" s="1">
         <v>0.19</v>
       </c>
@@ -2283,18 +2268,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.45">
-      <c r="A12" s="24"/>
-      <c r="B12" s="37"/>
-      <c r="C12" s="35"/>
-      <c r="D12" s="28"/>
+    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A12" s="62"/>
+      <c r="B12" s="56"/>
+      <c r="C12" s="54"/>
+      <c r="D12" s="64"/>
       <c r="E12" s="3" t="s">
         <v>44</v>
       </c>
       <c r="F12" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="G12" s="32"/>
+      <c r="G12" s="51"/>
       <c r="H12" s="1">
         <v>308.89999999999998</v>
       </c>
@@ -2319,7 +2304,7 @@
       <c r="O12" s="4">
         <v>3389.6645272576002</v>
       </c>
-      <c r="P12" s="53"/>
+      <c r="P12" s="47"/>
       <c r="Q12" s="4">
         <v>38626.409729214516</v>
       </c>
@@ -2327,8 +2312,8 @@
         <v>0.15</v>
       </c>
       <c r="S12" s="4"/>
-      <c r="T12" s="32"/>
-      <c r="U12" s="32"/>
+      <c r="T12" s="51"/>
+      <c r="U12" s="51"/>
       <c r="V12" s="1">
         <v>0.13</v>
       </c>
@@ -2358,18 +2343,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.45">
-      <c r="A13" s="24"/>
-      <c r="B13" s="37"/>
-      <c r="C13" s="35"/>
-      <c r="D13" s="28"/>
+    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A13" s="62"/>
+      <c r="B13" s="56"/>
+      <c r="C13" s="54"/>
+      <c r="D13" s="64"/>
       <c r="E13" s="3" t="s">
         <v>45</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="G13" s="32"/>
+      <c r="G13" s="51"/>
       <c r="H13" s="1">
         <v>267.5</v>
       </c>
@@ -2394,7 +2379,7 @@
       <c r="O13" s="4">
         <v>3825.1662000000006</v>
       </c>
-      <c r="P13" s="53"/>
+      <c r="P13" s="47"/>
       <c r="Q13" s="4">
         <v>43589.103209302339</v>
       </c>
@@ -2402,8 +2387,8 @@
         <v>0.15</v>
       </c>
       <c r="S13" s="4"/>
-      <c r="T13" s="32"/>
-      <c r="U13" s="32"/>
+      <c r="T13" s="51"/>
+      <c r="U13" s="51"/>
       <c r="V13" s="1">
         <v>0.23</v>
       </c>
@@ -2433,18 +2418,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.45">
-      <c r="A14" s="24"/>
-      <c r="B14" s="37"/>
-      <c r="C14" s="35"/>
-      <c r="D14" s="28"/>
+    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A14" s="62"/>
+      <c r="B14" s="56"/>
+      <c r="C14" s="54"/>
+      <c r="D14" s="64"/>
       <c r="E14" s="3" t="s">
         <v>46</v>
       </c>
       <c r="F14" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="G14" s="33"/>
+      <c r="G14" s="52"/>
       <c r="H14" s="1">
         <v>251.3</v>
       </c>
@@ -2469,7 +2454,7 @@
       <c r="O14" s="4">
         <v>4113.8844393359996</v>
       </c>
-      <c r="P14" s="54"/>
+      <c r="P14" s="48"/>
       <c r="Q14" s="4">
         <v>46879.148262200928</v>
       </c>
@@ -2477,8 +2462,8 @@
         <v>0.15</v>
       </c>
       <c r="S14" s="4"/>
-      <c r="T14" s="33"/>
-      <c r="U14" s="33"/>
+      <c r="T14" s="52"/>
+      <c r="U14" s="52"/>
       <c r="V14" s="1">
         <v>0.1</v>
       </c>
@@ -2510,24 +2495,11 @@
     </row>
   </sheetData>
   <mergeCells count="39">
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="AA1:AA2"/>
-    <mergeCell ref="Z1:Z2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="I1:I2"/>
-    <mergeCell ref="J1:J2"/>
-    <mergeCell ref="K1:K2"/>
-    <mergeCell ref="P3:P14"/>
-    <mergeCell ref="AB1:AB2"/>
-    <mergeCell ref="L1:L2"/>
-    <mergeCell ref="X1:X2"/>
-    <mergeCell ref="M1:M2"/>
-    <mergeCell ref="N1:N2"/>
-    <mergeCell ref="O1:O2"/>
-    <mergeCell ref="P1:P2"/>
-    <mergeCell ref="Q1:Q2"/>
-    <mergeCell ref="R1:R2"/>
+    <mergeCell ref="A3:A14"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="D3:D14"/>
+    <mergeCell ref="D1:D2"/>
     <mergeCell ref="G3:G14"/>
     <mergeCell ref="C3:C14"/>
     <mergeCell ref="B3:B14"/>
@@ -2544,11 +2516,24 @@
     <mergeCell ref="U3:U14"/>
     <mergeCell ref="Y1:Y2"/>
     <mergeCell ref="S1:S2"/>
-    <mergeCell ref="A3:A14"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="D3:D14"/>
-    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="P3:P14"/>
+    <mergeCell ref="AB1:AB2"/>
+    <mergeCell ref="L1:L2"/>
+    <mergeCell ref="X1:X2"/>
+    <mergeCell ref="M1:M2"/>
+    <mergeCell ref="N1:N2"/>
+    <mergeCell ref="O1:O2"/>
+    <mergeCell ref="P1:P2"/>
+    <mergeCell ref="Q1:Q2"/>
+    <mergeCell ref="R1:R2"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="AA1:AA2"/>
+    <mergeCell ref="Z1:Z2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:J2"/>
+    <mergeCell ref="K1:K2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2556,235 +2541,275 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3CDB956B-E27B-4860-9DB0-D7231D64BF21}">
-  <dimension ref="A1:H14"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <dimension ref="A1:I14"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="3" width="15.59765625" customWidth="1"/>
-    <col min="4" max="4" width="10.59765625" customWidth="1"/>
-    <col min="5" max="6" width="40.59765625" customWidth="1"/>
-    <col min="7" max="8" width="15.59765625" customWidth="1"/>
+    <col min="2" max="3" width="15.6640625" customWidth="1"/>
+    <col min="4" max="4" width="10.6640625" customWidth="1"/>
+    <col min="5" max="6" width="40.6640625" customWidth="1"/>
+    <col min="7" max="9" width="15.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A1" s="71" t="s">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1" s="78" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="71" t="s">
+      <c r="B1" s="78" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="71" t="s">
+      <c r="C1" s="78" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="71" t="s">
+      <c r="D1" s="78" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="71" t="s">
+      <c r="E1" s="78" t="s">
         <v>50</v>
       </c>
-      <c r="F1" s="73" t="s">
+      <c r="F1" s="80" t="s">
         <v>51</v>
       </c>
-      <c r="G1" s="58" t="s">
+      <c r="G1" s="65" t="s">
         <v>52</v>
       </c>
-      <c r="H1" s="60" t="s">
+      <c r="H1" s="31" t="s">
+        <v>4</v>
+      </c>
+      <c r="I1" s="67" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A2" s="72"/>
-      <c r="B2" s="72"/>
-      <c r="C2" s="72"/>
-      <c r="D2" s="72"/>
-      <c r="E2" s="72"/>
-      <c r="F2" s="74"/>
-      <c r="G2" s="59"/>
-      <c r="H2" s="61"/>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A3" s="62">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A2" s="79"/>
+      <c r="B2" s="79"/>
+      <c r="C2" s="79"/>
+      <c r="D2" s="79"/>
+      <c r="E2" s="79"/>
+      <c r="F2" s="81"/>
+      <c r="G2" s="66"/>
+      <c r="H2" s="82"/>
+      <c r="I2" s="68"/>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A3" s="69">
         <v>1</v>
       </c>
-      <c r="B3" s="64" t="s">
+      <c r="B3" s="71" t="s">
         <v>48</v>
       </c>
-      <c r="C3" s="12" t="s">
+      <c r="C3" s="22" t="s">
         <v>54</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="E3" s="67">
+      <c r="E3" s="74">
         <v>2000</v>
       </c>
-      <c r="F3" s="67">
+      <c r="F3" s="74">
         <v>4</v>
       </c>
-      <c r="G3" s="70">
+      <c r="G3" s="77">
         <v>700</v>
       </c>
-      <c r="H3" s="2">
+      <c r="H3" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I3" s="2">
         <v>800</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A4" s="19"/>
-      <c r="B4" s="17"/>
-      <c r="C4" s="13"/>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A4" s="29"/>
+      <c r="B4" s="27"/>
+      <c r="C4" s="23"/>
       <c r="D4" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="E4" s="68"/>
-      <c r="F4" s="68"/>
-      <c r="G4" s="13"/>
-      <c r="H4" s="2">
+      <c r="E4" s="75"/>
+      <c r="F4" s="75"/>
+      <c r="G4" s="23"/>
+      <c r="H4" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="I4" s="2">
         <v>700</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A5" s="19"/>
-      <c r="B5" s="17"/>
-      <c r="C5" s="13"/>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A5" s="29"/>
+      <c r="B5" s="27"/>
+      <c r="C5" s="23"/>
       <c r="D5" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="E5" s="68"/>
-      <c r="F5" s="68"/>
-      <c r="G5" s="13"/>
-      <c r="H5" s="2">
+      <c r="E5" s="75"/>
+      <c r="F5" s="75"/>
+      <c r="G5" s="23"/>
+      <c r="H5" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="I5" s="2">
         <v>600</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A6" s="19"/>
-      <c r="B6" s="17"/>
-      <c r="C6" s="13"/>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A6" s="29"/>
+      <c r="B6" s="27"/>
+      <c r="C6" s="23"/>
       <c r="D6" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="E6" s="68"/>
-      <c r="F6" s="68"/>
-      <c r="G6" s="13"/>
-      <c r="H6" s="2">
+      <c r="E6" s="75"/>
+      <c r="F6" s="75"/>
+      <c r="G6" s="23"/>
+      <c r="H6" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="I6" s="2">
         <v>500</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A7" s="19"/>
-      <c r="B7" s="17"/>
-      <c r="C7" s="13"/>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A7" s="29"/>
+      <c r="B7" s="27"/>
+      <c r="C7" s="23"/>
       <c r="D7" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="E7" s="68"/>
-      <c r="F7" s="68"/>
-      <c r="G7" s="13"/>
-      <c r="H7" s="2">
+      <c r="E7" s="75"/>
+      <c r="F7" s="75"/>
+      <c r="G7" s="23"/>
+      <c r="H7" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="I7" s="2">
         <v>400</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A8" s="19"/>
-      <c r="B8" s="17"/>
-      <c r="C8" s="13"/>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A8" s="29"/>
+      <c r="B8" s="27"/>
+      <c r="C8" s="23"/>
       <c r="D8" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="E8" s="68"/>
-      <c r="F8" s="68"/>
-      <c r="G8" s="13"/>
-      <c r="H8" s="2">
+      <c r="E8" s="75"/>
+      <c r="F8" s="75"/>
+      <c r="G8" s="23"/>
+      <c r="H8" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="I8" s="2">
         <v>400</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A9" s="19"/>
-      <c r="B9" s="17"/>
-      <c r="C9" s="13"/>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A9" s="29"/>
+      <c r="B9" s="27"/>
+      <c r="C9" s="23"/>
       <c r="D9" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="E9" s="68"/>
-      <c r="F9" s="68"/>
-      <c r="G9" s="13"/>
-      <c r="H9" s="2">
+      <c r="E9" s="75"/>
+      <c r="F9" s="75"/>
+      <c r="G9" s="23"/>
+      <c r="H9" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="I9" s="2">
         <v>300</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A10" s="19"/>
-      <c r="B10" s="17"/>
-      <c r="C10" s="13"/>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A10" s="29"/>
+      <c r="B10" s="27"/>
+      <c r="C10" s="23"/>
       <c r="D10" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="E10" s="68"/>
-      <c r="F10" s="68"/>
-      <c r="G10" s="13"/>
-      <c r="H10" s="2">
+      <c r="E10" s="75"/>
+      <c r="F10" s="75"/>
+      <c r="G10" s="23"/>
+      <c r="H10" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="I10" s="2">
         <v>400</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A11" s="19"/>
-      <c r="B11" s="17"/>
-      <c r="C11" s="13"/>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A11" s="29"/>
+      <c r="B11" s="27"/>
+      <c r="C11" s="23"/>
       <c r="D11" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="E11" s="68"/>
-      <c r="F11" s="68"/>
-      <c r="G11" s="13"/>
-      <c r="H11" s="2">
+      <c r="E11" s="75"/>
+      <c r="F11" s="75"/>
+      <c r="G11" s="23"/>
+      <c r="H11" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="I11" s="2">
         <v>500</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A12" s="19"/>
-      <c r="B12" s="17"/>
-      <c r="C12" s="13"/>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A12" s="29"/>
+      <c r="B12" s="27"/>
+      <c r="C12" s="23"/>
       <c r="D12" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="E12" s="68"/>
-      <c r="F12" s="68"/>
-      <c r="G12" s="13"/>
-      <c r="H12" s="2">
+      <c r="E12" s="75"/>
+      <c r="F12" s="75"/>
+      <c r="G12" s="23"/>
+      <c r="H12" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="I12" s="2">
         <v>600</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A13" s="19"/>
-      <c r="B13" s="17"/>
-      <c r="C13" s="13"/>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A13" s="29"/>
+      <c r="B13" s="27"/>
+      <c r="C13" s="23"/>
       <c r="D13" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="E13" s="68"/>
-      <c r="F13" s="68"/>
-      <c r="G13" s="13"/>
-      <c r="H13" s="2">
+      <c r="E13" s="75"/>
+      <c r="F13" s="75"/>
+      <c r="G13" s="23"/>
+      <c r="H13" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="I13" s="2">
         <v>700</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A14" s="63"/>
-      <c r="B14" s="65"/>
-      <c r="C14" s="66"/>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A14" s="70"/>
+      <c r="B14" s="72"/>
+      <c r="C14" s="73"/>
       <c r="D14" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="E14" s="69"/>
-      <c r="F14" s="69"/>
-      <c r="G14" s="66"/>
-      <c r="H14" s="2">
+      <c r="E14" s="76"/>
+      <c r="F14" s="76"/>
+      <c r="G14" s="73"/>
+      <c r="H14" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="I14" s="2">
         <v>700</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="14">
+  <mergeCells count="15">
     <mergeCell ref="G1:G2"/>
-    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
     <mergeCell ref="A3:A14"/>
     <mergeCell ref="B3:B14"/>
     <mergeCell ref="C3:C14"/>
@@ -2797,6 +2822,7 @@
     <mergeCell ref="D1:D2"/>
     <mergeCell ref="E1:E2"/>
     <mergeCell ref="F1:F2"/>
+    <mergeCell ref="H1:H2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -2806,44 +2832,44 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{456E5AAE-BDC2-4456-A449-5FA4DFB3DA6F}">
   <dimension ref="A1:F14"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="15.59765625" customWidth="1"/>
+    <col min="2" max="2" width="15.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A1" s="79" t="s">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="75" t="s">
+      <c r="B1" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="75" t="s">
+      <c r="C1" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="D1" s="75" t="s">
+      <c r="D1" s="17" t="s">
         <v>55</v>
       </c>
-      <c r="E1" s="75" t="s">
+      <c r="E1" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="F1" s="77" t="s">
+      <c r="F1" s="19" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A2" s="80"/>
-      <c r="B2" s="81"/>
-      <c r="C2" s="76"/>
-      <c r="D2" s="76"/>
-      <c r="E2" s="76"/>
-      <c r="F2" s="78"/>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A3" s="82">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A2" s="21"/>
+      <c r="B2" s="18"/>
+      <c r="C2" s="18"/>
+      <c r="D2" s="18"/>
+      <c r="E2" s="18"/>
+      <c r="F2" s="20"/>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A3" s="11">
         <v>1</v>
       </c>
-      <c r="B3" s="85" t="s">
+      <c r="B3" s="14" t="s">
         <v>48</v>
       </c>
       <c r="C3" s="3" t="s">
@@ -2855,13 +2881,13 @@
       <c r="E3" s="10">
         <v>7381.27</v>
       </c>
-      <c r="F3" s="11">
+      <c r="F3" s="2">
         <v>47614.903769945304</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A4" s="83"/>
-      <c r="B4" s="86"/>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A4" s="12"/>
+      <c r="B4" s="15"/>
       <c r="C4" s="3" t="s">
         <v>36</v>
       </c>
@@ -2871,13 +2897,13 @@
       <c r="E4" s="10">
         <v>6968.204299647713</v>
       </c>
-      <c r="F4" s="11">
+      <c r="F4" s="2">
         <v>53422.899630632463</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A5" s="83"/>
-      <c r="B5" s="86"/>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A5" s="12"/>
+      <c r="B5" s="15"/>
       <c r="C5" s="3" t="s">
         <v>37</v>
       </c>
@@ -2887,13 +2913,13 @@
       <c r="E5" s="10">
         <v>6888.0286444051526</v>
       </c>
-      <c r="F5" s="11">
+      <c r="F5" s="2">
         <v>52808.21960710617</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A6" s="83"/>
-      <c r="B6" s="86"/>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A6" s="12"/>
+      <c r="B6" s="15"/>
       <c r="C6" s="3" t="s">
         <v>38</v>
       </c>
@@ -2903,13 +2929,13 @@
       <c r="E6" s="10">
         <v>6628.93</v>
       </c>
-      <c r="F6" s="11">
+      <c r="F6" s="2">
         <v>39902.226056</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A7" s="83"/>
-      <c r="B7" s="86"/>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A7" s="12"/>
+      <c r="B7" s="15"/>
       <c r="C7" s="3" t="s">
         <v>39</v>
       </c>
@@ -2919,13 +2945,13 @@
       <c r="E7" s="10">
         <v>5916.7356971871632</v>
       </c>
-      <c r="F7" s="11">
+      <c r="F7" s="2">
         <v>45361.640345101587</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A8" s="83"/>
-      <c r="B8" s="86"/>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A8" s="12"/>
+      <c r="B8" s="15"/>
       <c r="C8" s="3" t="s">
         <v>40</v>
       </c>
@@ -2935,13 +2961,13 @@
       <c r="E8" s="10">
         <v>5486.5065000558125</v>
       </c>
-      <c r="F8" s="11">
+      <c r="F8" s="2">
         <v>42063.216500427894</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A9" s="83"/>
-      <c r="B9" s="86"/>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A9" s="12"/>
+      <c r="B9" s="15"/>
       <c r="C9" s="3" t="s">
         <v>41</v>
       </c>
@@ -2951,13 +2977,13 @@
       <c r="E9" s="10">
         <v>4996.1979985609678</v>
       </c>
-      <c r="F9" s="11">
+      <c r="F9" s="2">
         <v>38304.184655634082</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A10" s="83"/>
-      <c r="B10" s="86"/>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A10" s="12"/>
+      <c r="B10" s="15"/>
       <c r="C10" s="3" t="s">
         <v>42</v>
       </c>
@@ -2967,13 +2993,13 @@
       <c r="E10" s="10">
         <v>2808.7854808541579</v>
       </c>
-      <c r="F10" s="11">
+      <c r="F10" s="2">
         <v>21534.022019881879</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A11" s="83"/>
-      <c r="B11" s="86"/>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A11" s="12"/>
+      <c r="B11" s="15"/>
       <c r="C11" s="3" t="s">
         <v>43</v>
       </c>
@@ -2983,13 +3009,13 @@
       <c r="E11" s="10">
         <v>3728.83</v>
       </c>
-      <c r="F11" s="11">
+      <c r="F11" s="2">
         <v>29594.216612992743</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A12" s="83"/>
-      <c r="B12" s="86"/>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A12" s="12"/>
+      <c r="B12" s="15"/>
       <c r="C12" s="3" t="s">
         <v>44</v>
       </c>
@@ -2999,13 +3025,13 @@
       <c r="E12" s="10">
         <v>5793.9614593821771</v>
       </c>
-      <c r="F12" s="11">
+      <c r="F12" s="2">
         <v>44420.371188596691</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A13" s="83"/>
-      <c r="B13" s="86"/>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A13" s="12"/>
+      <c r="B13" s="15"/>
       <c r="C13" s="3" t="s">
         <v>45</v>
       </c>
@@ -3015,13 +3041,13 @@
       <c r="E13" s="10">
         <v>6538.3654813953508</v>
       </c>
-      <c r="F13" s="11">
+      <c r="F13" s="2">
         <v>50127.468690697686</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A14" s="84"/>
-      <c r="B14" s="87"/>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A14" s="13"/>
+      <c r="B14" s="16"/>
       <c r="C14" s="3" t="s">
         <v>46</v>
       </c>
@@ -3031,20 +3057,20 @@
       <c r="E14" s="10">
         <v>7031.8722393301387</v>
       </c>
-      <c r="F14" s="11">
+      <c r="F14" s="2">
         <v>53911.020501531064</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="8">
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
     <mergeCell ref="A3:A14"/>
     <mergeCell ref="B3:B14"/>
     <mergeCell ref="C1:C2"/>
     <mergeCell ref="D1:D2"/>
     <mergeCell ref="E1:E2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
